--- a/artfynd/A 14301-2022 artfynd.xlsx
+++ b/artfynd/A 14301-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14301-2022 artfynd.xlsx
+++ b/artfynd/A 14301-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2039,6 +2039,819 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120341787</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579550</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7056072</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120341904</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579522</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7056091</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120341660</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95225</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579599</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7056040</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120341450</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579561</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7056120</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120342395</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>579466</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7056251</v>
+      </c>
+      <c r="S18" t="n">
+        <v>18</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120342376</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>579469</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7056242</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120342472</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>579451</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7056298</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14301-2022 artfynd.xlsx
+++ b/artfynd/A 14301-2022 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120341787</v>
+        <v>120342376</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,16 +2057,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2082,14 +2082,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579550</v>
+        <v>579469</v>
       </c>
       <c r="R14" t="n">
-        <v>7056072</v>
+        <v>7056242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120341904</v>
+        <v>120342472</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,35 +2170,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2207,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579522</v>
+        <v>579451</v>
       </c>
       <c r="R15" t="n">
-        <v>7056091</v>
+        <v>7056298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2252,7 +2248,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120341660</v>
+        <v>120341904</v>
       </c>
       <c r="B16" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,38 +2287,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579599</v>
+        <v>579522</v>
       </c>
       <c r="R16" t="n">
-        <v>7056040</v>
+        <v>7056091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120341450</v>
+        <v>120342395</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,37 +2412,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579561</v>
+        <v>579466</v>
       </c>
       <c r="R17" t="n">
-        <v>7056120</v>
+        <v>7056251</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2466,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2476,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120342395</v>
+        <v>120341660</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>95225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,46 +2525,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579466</v>
+        <v>579599</v>
       </c>
       <c r="R18" t="n">
-        <v>7056251</v>
+        <v>7056040</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2583,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2593,7 +2598,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120342376</v>
+        <v>120341787</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,16 +2641,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2661,14 +2666,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579469</v>
+        <v>579550</v>
       </c>
       <c r="R19" t="n">
-        <v>7056242</v>
+        <v>7056072</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120342472</v>
+        <v>120341450</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2753,39 +2758,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579451</v>
+        <v>579561</v>
       </c>
       <c r="R20" t="n">
-        <v>7056298</v>
+        <v>7056120</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 14301-2022 artfynd.xlsx
+++ b/artfynd/A 14301-2022 artfynd.xlsx
@@ -2158,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120342472</v>
+        <v>120341450</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,39 +2174,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579451</v>
+        <v>579561</v>
       </c>
       <c r="R15" t="n">
-        <v>7056298</v>
+        <v>7056120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120341904</v>
+        <v>120341660</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,47 +2282,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579522</v>
+        <v>579599</v>
       </c>
       <c r="R16" t="n">
-        <v>7056091</v>
+        <v>7056040</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2345,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2355,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2513,10 +2499,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120341660</v>
+        <v>120341904</v>
       </c>
       <c r="B18" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2525,38 +2511,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579599</v>
+        <v>579522</v>
       </c>
       <c r="R18" t="n">
-        <v>7056040</v>
+        <v>7056091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2583,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2593,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120341787</v>
+        <v>120342472</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,16 +2636,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2666,14 +2661,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579550</v>
+        <v>579451</v>
       </c>
       <c r="R19" t="n">
-        <v>7056072</v>
+        <v>7056298</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,10 +2737,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120341450</v>
+        <v>120341787</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,34 +2753,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579561</v>
+        <v>579550</v>
       </c>
       <c r="R20" t="n">
-        <v>7056120</v>
+        <v>7056072</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 14301-2022 artfynd.xlsx
+++ b/artfynd/A 14301-2022 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120342376</v>
+        <v>120341450</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,39 +2057,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579469</v>
+        <v>579561</v>
       </c>
       <c r="R14" t="n">
-        <v>7056242</v>
+        <v>7056120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120341450</v>
+        <v>120341787</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,34 +2169,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579561</v>
+        <v>579550</v>
       </c>
       <c r="R15" t="n">
-        <v>7056120</v>
+        <v>7056072</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120341660</v>
+        <v>120341904</v>
       </c>
       <c r="B16" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,38 +2282,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579599</v>
+        <v>579522</v>
       </c>
       <c r="R16" t="n">
-        <v>7056040</v>
+        <v>7056091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,7 +2354,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2355,7 +2364,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,7 +2391,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120342395</v>
+        <v>120342472</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2427,13 +2436,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579466</v>
+        <v>579451</v>
       </c>
       <c r="R17" t="n">
-        <v>7056251</v>
+        <v>7056298</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2462,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2472,7 +2481,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120341904</v>
+        <v>120342376</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,35 +2520,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2548,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579522</v>
+        <v>579469</v>
       </c>
       <c r="R18" t="n">
-        <v>7056091</v>
+        <v>7056242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2593,7 +2598,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,7 +2625,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120342472</v>
+        <v>120342395</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2665,13 +2670,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579451</v>
+        <v>579466</v>
       </c>
       <c r="R19" t="n">
-        <v>7056298</v>
+        <v>7056251</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2700,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120341787</v>
+        <v>120341660</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>95225</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2749,43 +2754,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579550</v>
+        <v>579599</v>
       </c>
       <c r="R20" t="n">
-        <v>7056072</v>
+        <v>7056040</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 14301-2022 artfynd.xlsx
+++ b/artfynd/A 14301-2022 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120341450</v>
+        <v>120342395</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,37 +2057,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579561</v>
+        <v>579466</v>
       </c>
       <c r="R14" t="n">
-        <v>7056120</v>
+        <v>7056251</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120341787</v>
+        <v>120341450</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,39 +2174,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579550</v>
+        <v>579561</v>
       </c>
       <c r="R15" t="n">
-        <v>7056072</v>
+        <v>7056120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120341904</v>
+        <v>120342376</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,35 +2282,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2319,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579522</v>
+        <v>579469</v>
       </c>
       <c r="R16" t="n">
-        <v>7056091</v>
+        <v>7056242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2350,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2360,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120342472</v>
+        <v>120341904</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,31 +2399,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579451</v>
+        <v>579522</v>
       </c>
       <c r="R17" t="n">
-        <v>7056298</v>
+        <v>7056091</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,7 +2508,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120342376</v>
+        <v>120342472</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579469</v>
+        <v>579451</v>
       </c>
       <c r="R18" t="n">
-        <v>7056242</v>
+        <v>7056298</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120342395</v>
+        <v>120341660</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>95225</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,46 +2637,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579466</v>
+        <v>579599</v>
       </c>
       <c r="R19" t="n">
-        <v>7056251</v>
+        <v>7056040</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,10 +2737,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120341660</v>
+        <v>120341787</v>
       </c>
       <c r="B20" t="n">
-        <v>95225</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,38 +2749,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579599</v>
+        <v>579550</v>
       </c>
       <c r="R20" t="n">
-        <v>7056040</v>
+        <v>7056072</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 14301-2022 artfynd.xlsx
+++ b/artfynd/A 14301-2022 artfynd.xlsx
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120342395</v>
+        <v>120342472</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579466</v>
+        <v>579451</v>
       </c>
       <c r="R14" t="n">
-        <v>7056251</v>
+        <v>7056298</v>
       </c>
       <c r="S14" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120341450</v>
+        <v>120341787</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,34 +2174,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579561</v>
+        <v>579550</v>
       </c>
       <c r="R15" t="n">
-        <v>7056120</v>
+        <v>7056072</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,7 +2248,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120341904</v>
+        <v>120342395</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,35 +2404,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2436,13 +2437,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579522</v>
+        <v>579466</v>
       </c>
       <c r="R17" t="n">
-        <v>7056091</v>
+        <v>7056251</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2471,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2482,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120342472</v>
+        <v>120341450</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,39 +2525,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579451</v>
+        <v>579561</v>
       </c>
       <c r="R18" t="n">
-        <v>7056298</v>
+        <v>7056120</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,10 +2621,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120341660</v>
+        <v>120341904</v>
       </c>
       <c r="B19" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,38 +2633,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579599</v>
+        <v>579522</v>
       </c>
       <c r="R19" t="n">
-        <v>7056040</v>
+        <v>7056091</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120341787</v>
+        <v>120341660</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>95225</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2749,43 +2754,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579550</v>
+        <v>579599</v>
       </c>
       <c r="R20" t="n">
-        <v>7056072</v>
+        <v>7056040</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 14301-2022 artfynd.xlsx
+++ b/artfynd/A 14301-2022 artfynd.xlsx
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120342472</v>
+        <v>120342376</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579451</v>
+        <v>579469</v>
       </c>
       <c r="R14" t="n">
-        <v>7056298</v>
+        <v>7056242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120341787</v>
+        <v>120341450</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,39 +2174,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579550</v>
+        <v>579561</v>
       </c>
       <c r="R15" t="n">
-        <v>7056072</v>
+        <v>7056120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,7 +2270,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120342376</v>
+        <v>120342395</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2320,13 +2315,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579469</v>
+        <v>579466</v>
       </c>
       <c r="R16" t="n">
-        <v>7056242</v>
+        <v>7056251</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2350,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2360,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120342395</v>
+        <v>120342472</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2437,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579466</v>
+        <v>579451</v>
       </c>
       <c r="R17" t="n">
-        <v>7056251</v>
+        <v>7056298</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2472,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120341450</v>
+        <v>120341904</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,38 +2516,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579561</v>
+        <v>579522</v>
       </c>
       <c r="R18" t="n">
-        <v>7056120</v>
+        <v>7056091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2598,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120341904</v>
+        <v>120341660</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,47 +2637,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579522</v>
+        <v>579599</v>
       </c>
       <c r="R19" t="n">
-        <v>7056091</v>
+        <v>7056040</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,10 +2737,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120341660</v>
+        <v>120341787</v>
       </c>
       <c r="B20" t="n">
-        <v>95225</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,38 +2749,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579599</v>
+        <v>579550</v>
       </c>
       <c r="R20" t="n">
-        <v>7056040</v>
+        <v>7056072</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 14301-2022 artfynd.xlsx
+++ b/artfynd/A 14301-2022 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120342376</v>
+        <v>120341904</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,31 +2053,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2086,10 +2090,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579469</v>
+        <v>579522</v>
       </c>
       <c r="R14" t="n">
-        <v>7056242</v>
+        <v>7056091</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120341450</v>
+        <v>120341660</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>95225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,38 +2174,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579561</v>
+        <v>579599</v>
       </c>
       <c r="R15" t="n">
-        <v>7056120</v>
+        <v>7056040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120342395</v>
+        <v>120341450</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,42 +2290,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579466</v>
+        <v>579561</v>
       </c>
       <c r="R16" t="n">
-        <v>7056251</v>
+        <v>7056120</v>
       </c>
       <c r="S16" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2360,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2504,10 +2503,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120341904</v>
+        <v>120342376</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,35 +2515,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2553,10 +2548,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579522</v>
+        <v>579469</v>
       </c>
       <c r="R18" t="n">
-        <v>7056091</v>
+        <v>7056242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2583,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2593,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120341660</v>
+        <v>120342395</v>
       </c>
       <c r="B19" t="n">
-        <v>95225</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,41 +2632,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579599</v>
+        <v>579466</v>
       </c>
       <c r="R19" t="n">
-        <v>7056040</v>
+        <v>7056251</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
